--- a/tool/macro/macros/原価管理シート_Append.xlsx
+++ b/tool/macro/macros/原価管理シート_Append.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\macro\macros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE57B3C4-33D3-4F0C-A612-5BEDB9DF1A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83E573C-62EA-4C73-AD23-AD34170FAC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB947460-3F26-4FCB-8BB8-02F93A399293}"/>
   </bookViews>
@@ -25,67 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
-  <si>
-    <t>実績Excel</t>
-    <rPh sb="0" eb="2">
-      <t>ジッセキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>原価管理Excel</t>
-    <rPh sb="0" eb="4">
-      <t>ゲンカカンリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>会計区分1マッピング</t>
-    <rPh sb="0" eb="4">
-      <t>カイケイクブン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>会計区分2マッピング</t>
-    <rPh sb="0" eb="4">
-      <t>カイケイクブン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>実績Excel貼付範囲</t>
-    <rPh sb="0" eb="2">
-      <t>ジッセキ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ハ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ハンイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>原価管理Excel貼付範囲</t>
-    <rPh sb="0" eb="4">
-      <t>ゲンカカンリ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ハ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ハンイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
   <si>
     <t>年度</t>
     <rPh sb="0" eb="2">
@@ -259,6 +199,61 @@
   <si>
     <t>S</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>会計区分1マッピング</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実績シート-項目</t>
+    <rPh sb="0" eb="2">
+      <t>ジッセキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>計算算定シート-項目</t>
+    <rPh sb="0" eb="2">
+      <t>ケイサン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サンテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実績シート-対象範囲</t>
+    <rPh sb="0" eb="2">
+      <t>ジッセキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>計算算定シート-対象範囲</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>会計区分2マッピング</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実績シート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>計算算定シート</t>
   </si>
 </sst>
 </file>
@@ -282,7 +277,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -292,6 +287,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -364,7 +365,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -378,6 +379,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -694,165 +704,182 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD873C71-84D5-4CAD-A47B-ED09E373229A}">
-  <dimension ref="B2:R8"/>
+  <dimension ref="B1:R8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="7.5" customWidth="1"/>
     <col min="2" max="2" width="9.796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.59765625" customWidth="1"/>
-    <col min="12" max="12" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="N1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
     <row r="2" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B2" s="3" t="s">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C2" s="4"/>
       <c r="E2" s="3" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="F2" s="4"/>
       <c r="H2" s="3" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="I2" s="4"/>
       <c r="K2" s="3" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="L2" s="4"/>
-      <c r="N2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O2" s="4"/>
-      <c r="Q2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R2" s="4"/>
+      <c r="N2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="7"/>
+      <c r="Q2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="R2" s="7"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K3" s="1">
+      <c r="N3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>12</v>
+      <c r="Q3" s="1">
+        <v>4</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="2">
+      <c r="N4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q4" s="2">
         <v>9</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="R4" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q5" s="2">
         <v>10</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>27</v>
+      <c r="R5" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.45">
       <c r="E7" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.45">
       <c r="E8" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/tool/macro/macros/原価管理シート_Append.xlsx
+++ b/tool/macro/macros/原価管理シート_Append.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\macro\macros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83E573C-62EA-4C73-AD23-AD34170FAC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52525347-3BF4-43BB-A7F0-40A866F5B061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB947460-3F26-4FCB-8BB8-02F93A399293}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
   <si>
     <t>年度</t>
     <rPh sb="0" eb="2">
@@ -63,13 +63,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>開始</t>
-    <rPh sb="0" eb="2">
-      <t>カイシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>AJ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -114,25 +107,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>終了</t>
-    <rPh sb="0" eb="2">
-      <t>シュウリョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>AV</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>AG</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>区分</t>
-    <rPh sb="0" eb="2">
-      <t>クブン</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -157,35 +136,14 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>原価区分ID</t>
-    <rPh sb="0" eb="4">
-      <t>ゲンカクブン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>AH</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>会計区分1</t>
-    <rPh sb="0" eb="4">
-      <t>カイケイクブン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Q</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>会計区分2</t>
-    <rPh sb="0" eb="4">
-      <t>カイケイクブン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>R</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -201,59 +159,105 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>会計区分1マッピング</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>実績シート-項目</t>
+    <t>実績シート</t>
     <rPh sb="0" eb="2">
       <t>ジッセキ</t>
     </rPh>
-    <rPh sb="6" eb="8">
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>計算算定シート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>項目名</t>
+    <rPh sb="0" eb="2">
       <t>コウモク</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>計算算定シート-項目</t>
-    <rPh sb="0" eb="2">
-      <t>ケイサン</t>
+    <rPh sb="2" eb="3">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>区分1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>区分2</t>
+    <rPh sb="0" eb="2">
+      <t>クブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>対象範囲-開始列</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
     </rPh>
     <rPh sb="2" eb="4">
-      <t>サンテイ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>レツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>対象範囲-終了列</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>レツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>対象範囲-開始行</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ギョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>項目マッピング</t>
+    <rPh sb="0" eb="2">
       <t>コウモク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>実績シート-対象範囲</t>
-    <rPh sb="0" eb="2">
-      <t>ジッセキ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ハンイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>計算算定シート-対象範囲</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>会計区分2マッピング</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>実績シート</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>計算算定シート</t>
+    <t>データマッピング-区分1</t>
+    <rPh sb="0" eb="12">
+      <t>クブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データマッピング-区分2</t>
+    <rPh sb="0" eb="12">
+      <t>クブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -277,7 +281,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -290,45 +294,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -365,29 +337,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -704,182 +664,180 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD873C71-84D5-4CAD-A47B-ED09E373229A}">
-  <dimension ref="B1:R8"/>
+  <dimension ref="B2:J12"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="7.5" customWidth="1"/>
-    <col min="2" max="2" width="9.796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.59765625" customWidth="1"/>
-    <col min="14" max="14" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.3984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.09765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36" customWidth="1"/>
+    <col min="12" max="12" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="N1" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q1" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="R1" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="B2" s="3" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="E2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="4"/>
-      <c r="H2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="4"/>
-      <c r="K2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" s="4"/>
-      <c r="N2" s="5" t="s">
+      <c r="C4" s="1">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1">
+        <v>5</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4" s="1">
+        <v>4</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="1">
+        <v>9</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O2" s="7"/>
-      <c r="Q2" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="R2" s="7"/>
-    </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="B3" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="1">
+        <v>10</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L3" s="1" t="s">
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q3" s="1">
-        <v>4</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="B4" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="2" t="s">
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>9</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="B5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="D10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q5" s="2">
-        <v>10</v>
-      </c>
-      <c r="R5" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="B6" s="2" t="s">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="E7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="E8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/tool/macro/macros/原価管理シート_Append.xlsx
+++ b/tool/macro/macros/原価管理シート_Append.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\macro\macros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52525347-3BF4-43BB-A7F0-40A866F5B061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527A8928-22E2-409F-83D0-9118583B69FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB947460-3F26-4FCB-8BB8-02F93A399293}"/>
   </bookViews>
@@ -295,25 +295,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -337,14 +324,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
@@ -668,13 +652,9 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="7.5" customWidth="1"/>
-    <col min="2" max="2" width="16.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.09765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.19921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.19921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36" customWidth="1"/>
+    <col min="2" max="4" width="20.69921875" customWidth="1"/>
+    <col min="6" max="7" width="20.69921875" customWidth="1"/>
+    <col min="9" max="10" width="20.69921875" customWidth="1"/>
     <col min="12" max="12" width="19.3984375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.3984375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="19.3984375" bestFit="1" customWidth="1"/>
@@ -708,10 +688,10 @@
       <c r="G3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>25</v>
       </c>
     </row>

--- a/tool/macro/macros/原価管理シート_Append.xlsx
+++ b/tool/macro/macros/原価管理シート_Append.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\macro\macros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527A8928-22E2-409F-83D0-9118583B69FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87BFB1BA-2F19-494A-86C0-620DF3B0645C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB947460-3F26-4FCB-8BB8-02F93A399293}"/>
   </bookViews>
@@ -264,7 +264,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -280,8 +280,17 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -291,6 +300,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -324,14 +339,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -662,163 +683,163 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C4" s="1">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1">
         <v>2</v>
       </c>
-      <c r="D4" s="1">
+      <c r="F4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="J4" s="1">
         <v>4</v>
       </c>
-      <c r="I4" s="1">
-        <v>4</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="F5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="1">
+      <c r="I5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="1">
         <v>9</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="I6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B7" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="1">
-        <v>10</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>20</v>
-      </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="D12" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/tool/macro/macros/原価管理シート_Append.xlsx
+++ b/tool/macro/macros/原価管理シート_Append.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\macro\macros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87BFB1BA-2F19-494A-86C0-620DF3B0645C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62FF4DA-2333-45A2-9235-01AAA188C98F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB947460-3F26-4FCB-8BB8-02F93A399293}"/>
   </bookViews>
@@ -698,22 +698,22 @@
         <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
@@ -721,22 +721,22 @@
         <v>31</v>
       </c>
       <c r="C4" s="1">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1">
         <v>5</v>
       </c>
-      <c r="D4" s="1">
-        <v>2</v>
-      </c>
       <c r="F4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="1">
+        <v>4</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="J4" s="1">
-        <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.45">
@@ -744,22 +744,22 @@
         <v>29</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="F5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="1">
+        <v>9</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="J5" s="1">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.45">
@@ -767,16 +767,16 @@
         <v>30</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="1">
+        <v>10</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="J6" s="1">
-        <v>10</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.45">
@@ -784,10 +784,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
@@ -795,30 +795,30 @@
         <v>8</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="1"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
@@ -826,20 +826,20 @@
         <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/tool/macro/macros/原価管理シート_Append.xlsx
+++ b/tool/macro/macros/原価管理シート_Append.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\macro\macros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62FF4DA-2333-45A2-9235-01AAA188C98F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C52D22FF-9D77-4385-B9A6-10A1D57A758F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB947460-3F26-4FCB-8BB8-02F93A399293}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
   <si>
     <t>年度</t>
     <rPh sb="0" eb="2">
@@ -191,54 +191,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>対象範囲-開始列</t>
-    <rPh sb="0" eb="2">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ハンイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>カイシ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>レツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>対象範囲-終了列</t>
-    <rPh sb="0" eb="2">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ハンイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>シュウリョウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>レツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>対象範囲-開始行</t>
-    <rPh sb="0" eb="2">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ハンイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>カイシ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ギョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>項目マッピング</t>
     <rPh sb="0" eb="2">
       <t>コウモク</t>
@@ -256,6 +208,43 @@
     <t>データマッピング-区分2</t>
     <rPh sb="0" eb="12">
       <t>クブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開始行</t>
+    <rPh sb="0" eb="2">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ギョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開始列</t>
+    <rPh sb="0" eb="2">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>レツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>終了列</t>
+    <rPh sb="0" eb="2">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>レツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>範囲マッピング</t>
+    <rPh sb="0" eb="2">
+      <t>ハンイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -669,31 +658,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD873C71-84D5-4CAD-A47B-ED09E373229A}">
-  <dimension ref="B2:J12"/>
+  <dimension ref="B2:N9"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="7.5" customWidth="1"/>
-    <col min="2" max="4" width="20.69921875" customWidth="1"/>
-    <col min="6" max="7" width="20.69921875" customWidth="1"/>
-    <col min="9" max="10" width="20.69921875" customWidth="1"/>
-    <col min="12" max="12" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.3984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.69921875" customWidth="1"/>
+    <col min="2" max="2" width="20.69921875" customWidth="1"/>
+    <col min="3" max="4" width="15.69921875" customWidth="1"/>
+    <col min="5" max="5" width="5.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="8" width="15.69921875" customWidth="1"/>
+    <col min="9" max="9" width="5.69921875" customWidth="1"/>
+    <col min="10" max="11" width="20.69921875" customWidth="1"/>
+    <col min="12" max="12" width="5.69921875" customWidth="1"/>
+    <col min="13" max="14" width="20.69921875" customWidth="1"/>
+    <col min="16" max="16" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B2" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B3" s="3" t="s">
         <v>26</v>
       </c>
@@ -704,21 +702,30 @@
         <v>25</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="M3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B4" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="1">
         <v>2</v>
@@ -726,22 +733,31 @@
       <c r="D4" s="1">
         <v>5</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="1">
+      <c r="M4" s="1">
         <v>4</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B5" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
@@ -749,22 +765,31 @@
       <c r="D5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="1">
+      <c r="M5" s="1">
         <v>9</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B6" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>14</v>
@@ -772,72 +797,48 @@
       <c r="D6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="1">
+      <c r="F6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M6" s="1">
         <v>10</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="N6" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B7" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>2</v>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="F7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>10</v>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="F8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B10" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B12" s="4" t="s">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="F9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
+      <c r="G9" s="1"/>
+      <c r="H9" s="1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/tool/macro/macros/原価管理シート_Append.xlsx
+++ b/tool/macro/macros/原価管理シート_Append.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\macro\macros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C52D22FF-9D77-4385-B9A6-10A1D57A758F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAE8FC2-F08B-420E-9CC2-32E4F21D1C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB947460-3F26-4FCB-8BB8-02F93A399293}"/>
   </bookViews>
@@ -198,20 +198,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>データマッピング-区分1</t>
-    <rPh sb="0" eb="12">
-      <t>クブン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>データマッピング-区分2</t>
-    <rPh sb="0" eb="12">
-      <t>クブン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>開始行</t>
     <rPh sb="0" eb="2">
       <t>カイシ</t>
@@ -245,6 +231,26 @@
     <t>範囲マッピング</t>
     <rPh sb="0" eb="2">
       <t>ハンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>変換マッピング-区分1</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンカン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>クブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>変換マッピング-区分2</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンカン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>クブン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -679,16 +685,16 @@
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B2" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>29</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.45">
@@ -725,7 +731,7 @@
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B4" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1">
         <v>2</v>
@@ -757,7 +763,7 @@
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B5" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
@@ -789,7 +795,7 @@
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B6" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>14</v>

--- a/tool/macro/macros/原価管理シート_Append.xlsx
+++ b/tool/macro/macros/原価管理シート_Append.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\macro\macros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAE8FC2-F08B-420E-9CC2-32E4F21D1C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809DC719-B407-4F53-A952-492345DFFF23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB947460-3F26-4FCB-8BB8-02F93A399293}"/>
   </bookViews>
   <sheets>
-    <sheet name="システム用" sheetId="1" r:id="rId1"/>
+    <sheet name="ツール設定用" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
